--- a/artfynd/A 64575-2023 artfynd.xlsx
+++ b/artfynd/A 64575-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64575-2023 artfynd.xlsx
+++ b/artfynd/A 64575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112164211</v>
       </c>
       <c r="B2" t="n">
-        <v>90215</v>
+        <v>90225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>112199353</v>
       </c>
       <c r="B3" t="n">
-        <v>90211</v>
+        <v>90221</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 64575-2023 artfynd.xlsx
+++ b/artfynd/A 64575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112164211</v>
       </c>
       <c r="B2" t="n">
-        <v>90225</v>
+        <v>90237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>112199353</v>
       </c>
       <c r="B3" t="n">
-        <v>90221</v>
+        <v>90233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 64575-2023 artfynd.xlsx
+++ b/artfynd/A 64575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112164211</v>
       </c>
       <c r="B2" t="n">
-        <v>90237</v>
+        <v>90238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>112199353</v>
       </c>
       <c r="B3" t="n">
-        <v>90233</v>
+        <v>90234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 64575-2023 artfynd.xlsx
+++ b/artfynd/A 64575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112164211</v>
       </c>
       <c r="B2" t="n">
-        <v>90238</v>
+        <v>90241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>112199353</v>
       </c>
       <c r="B3" t="n">
-        <v>90234</v>
+        <v>90237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 64575-2023 artfynd.xlsx
+++ b/artfynd/A 64575-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>112199353</v>
       </c>
       <c r="B3" t="n">
-        <v>90237</v>
+        <v>90243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 64575-2023 artfynd.xlsx
+++ b/artfynd/A 64575-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>112199353</v>
       </c>
       <c r="B3" t="n">
-        <v>90243</v>
+        <v>90244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
